--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación ISAPRE</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:55</t>
+    <t xml:space="preserve">2026-08-28 15:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:12</t>
+    <t xml:space="preserve">2026-08-29 05:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:49</t>
+    <t xml:space="preserve">2026-09-07 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2024.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:11</t>
+    <t xml:space="preserve">2026-09-08 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
